--- a/invoice_system_management/static/excel/customer.xlsx
+++ b/invoice_system_management/static/excel/customer.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -438,11 +438,13 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -478,25 +480,35 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>is_GST_applied</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>product_id</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>product_name</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>product_price</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>product_amount</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>product_unit</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>customer_total</t>
         </is>
@@ -525,38 +537,47 @@
       <c r="F2" t="n">
         <v>472</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
         <v>2</v>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Cycle</t>
         </is>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>100</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>2</v>
       </c>
-      <c r="K2" t="n">
-        <v>1701.2978</v>
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
+        <v>2101.2978</v>
       </c>
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>3</v>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>bike</t>
         </is>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>200</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -571,18 +592,24 @@
       <c r="F6" t="n">
         <v>1182.6078</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6" t="b">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
         <v>2</v>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>Cycle</t>
         </is>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>1002.21</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -597,22 +624,80 @@
       <c r="F8" t="n">
         <v>46.69</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8" t="b">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
         <v>2</v>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>Cycle</t>
         </is>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>46.69</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="9"/>
+    <row r="10">
+      <c r="D10" t="n">
+        <v>10</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>45455</v>
+      </c>
+      <c r="F10" t="n">
+        <v>400</v>
+      </c>
+      <c r="G10" t="b">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Cycle</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>100</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="12">
+      <c r="H12" t="n">
+        <v>4</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>bat</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>100</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3</v>
+      </c>
+      <c r="L12" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
